--- a/src/main/resources/reports/plantilla_reporte_v1.xlsx
+++ b/src/main/resources/reports/plantilla_reporte_v1.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C316710-67E7-47CB-8548-4E8D125C9BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2565B5F2-F7FB-4F93-B1EA-4734CBC22A8E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,8 +23,48 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Jorge F. Coaquira Ramos</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author: Jorge F. Coaquira Ramos:
+jx:area(lastCell="L3")</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author: Jorge F. Coaquira Ramos:
+jx:each(items="bienes" var="bien" lastCell="L3")</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -61,13 +100,52 @@
   </si>
   <si>
     <t>MODELO</t>
+  </si>
+  <si>
+    <t>AÑO ADQUIRIDO</t>
+  </si>
+  <si>
+    <t>${bien.orden}</t>
+  </si>
+  <si>
+    <t>${bien.sede}</t>
+  </si>
+  <si>
+    <t>${bien.area}</t>
+  </si>
+  <si>
+    <t>${bien.codigoPatrimonial}</t>
+  </si>
+  <si>
+    <t>${bien.descripcion}</t>
+  </si>
+  <si>
+    <t>${bien.marca}</t>
+  </si>
+  <si>
+    <t>${bien.modelo}</t>
+  </si>
+  <si>
+    <t>${bien.serie}</t>
+  </si>
+  <si>
+    <t>${bien.conservacion}</t>
+  </si>
+  <si>
+    <t>${bien.anioAdquisicion}</t>
+  </si>
+  <si>
+    <t>${bien.empleado}</t>
+  </si>
+  <si>
+    <t>${bien.perfil}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +168,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -186,7 +271,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns="" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -577,24 +662,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6BFA51-2ED1-41AA-96F8-8196F73B7473}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" customWidth="1"/>
-    <col min="2" max="2" width="29.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="26.5546875" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="31.28515625" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -608,8 +693,9 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,17 +724,59 @@
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>